--- a/定额.xlsx
+++ b/定额.xlsx
@@ -7,27 +7,27 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="加长轴转子加工 C01 1900-01-01" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="同步电机 C02 1900-01-01" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="机座 C03 1900-01-01" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="机座 C03 2020-03-01" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="特殊电机装配 C04 2020-03-01" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="端盖 C05 1900-01-01" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="端盖 C05 2020-03-01" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="绕嵌排 C06 1900-01-01" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="绕嵌排 C06 2015-09-01" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="绕嵌排 C06 2016-11-01" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="绕嵌排 C06 2020-03-01" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="绕嵌排 C06 2020-12-01" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="绕嵌排 C06 2021-01-01" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="绕嵌排 C06 2021-10-01" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="绕嵌排 C06 2021-12-01" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="装配 C07 1900-01-01" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="装配 C07 2020-03-01" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="装配铁 C08 1900-01-01" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="转子 C09 2020-03-01" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="轴 C10 2020-03-01" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="轴转子 C11 1900-01-01" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="加长轴转子加工 A 1900-01-01" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="同步电机 B 1900-01-01" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="机座 C 1900-01-01" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="机座 C 2020-03-01" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="特殊电机装配 D 2020-03-01" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="端盖 E 1900-01-01" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="端盖 E 2020-03-01" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="绕嵌排 F 1900-01-01" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="绕嵌排 F 2015-09-01" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="绕嵌排 F 2016-11-01" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="绕嵌排 F 2020-03-01" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="绕嵌排 F 2020-12-01" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="绕嵌排 F 2021-01-01" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="绕嵌排 F 2021-10-01" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="绕嵌排 F 2021-12-01" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="装配 G 1900-01-01" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="装配 G 2020-03-01" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="装配铁 H 1900-01-01" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="转子 I 2020-03-01" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="轴 J 2020-03-01" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="轴转子 K 1900-01-01" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25887,7 +25887,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>Y2轴(普车)/徐州格迪电机轴 (Y2ZPCXZGDDJZ)</t>
+          <t>Y2轴(普车) (Y2ZPC)</t>
         </is>
       </c>
     </row>
@@ -26228,7 +26228,7 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>Y2轴(数控)/徐州格迪电机轴 (Y2ZSKXZGDDJZ)</t>
+          <t>Y2轴(数控) (Y2ZSK)</t>
         </is>
       </c>
     </row>
